--- a/연구코드/results/feature_selection/sinchon/step3_univariate.xlsx
+++ b/연구코드/results/feature_selection/sinchon/step3_univariate.xlsx
@@ -103,40 +103,40 @@
     <t>IQR</t>
   </si>
   <si>
+    <t>peak_last_pos</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>signal_energy</t>
+  </si>
+  <si>
+    <t>peak_std_height</t>
+  </si>
+  <si>
+    <t>peak_first_pos</t>
+  </si>
+  <si>
     <t>min</t>
   </si>
   <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>signal_energy</t>
-  </si>
-  <si>
-    <t>peak_std_height</t>
+    <t>peak_main_pos</t>
   </si>
   <si>
     <t>slope_std</t>
   </si>
   <si>
+    <t>slope_min</t>
+  </si>
+  <si>
+    <t>wavelet_cD3_std</t>
+  </si>
+  <si>
+    <t>band3_energy</t>
+  </si>
+  <si>
     <t>slope_mean</t>
-  </si>
-  <si>
-    <t>peak_last_pos</t>
-  </si>
-  <si>
-    <t>peak_main_pos</t>
-  </si>
-  <si>
-    <t>peak_first_pos</t>
-  </si>
-  <si>
-    <t>slope_min</t>
-  </si>
-  <si>
-    <t>band3_energy</t>
-  </si>
-  <si>
-    <t>wavelet_cD3_std</t>
   </si>
 </sst>
 </file>
@@ -578,7 +578,7 @@
         <v>0.1733840996662887</v>
       </c>
       <c r="D6">
-        <v>4.894997707133988E-10</v>
+        <v>4.894997707133989E-10</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -676,7 +676,7 @@
         <v>0.02520720991881296</v>
       </c>
       <c r="D13">
-        <v>0.3692266617451234</v>
+        <v>0.3692266617451235</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -816,7 +816,7 @@
         <v>-0.06016177884717459</v>
       </c>
       <c r="D23">
-        <v>0.03197962040409952</v>
+        <v>0.03197962040409953</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -869,10 +869,10 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>0.2311231494201107</v>
+        <v>0.02782971538947907</v>
       </c>
       <c r="D27">
-        <v>7.126123145518417E-17</v>
+        <v>0.3215023059479291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -886,7 +886,7 @@
         <v>-0.131354028217828</v>
       </c>
       <c r="D28">
-        <v>2.618507265846386E-06</v>
+        <v>2.618507265846387E-06</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -925,10 +925,10 @@
         <v>0</v>
       </c>
       <c r="C31">
-        <v>0.2045972503771621</v>
+        <v>-0.001178186297915739</v>
       </c>
       <c r="D31">
-        <v>1.771735228659869E-13</v>
+        <v>0.9665287451927558</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -939,10 +939,10 @@
         <v>0</v>
       </c>
       <c r="C32">
-        <v>0.06899528972260857</v>
+        <v>0.2311231494201107</v>
       </c>
       <c r="D32">
-        <v>0.01388328883776795</v>
+        <v>7.126123145518417E-17</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -953,10 +953,10 @@
         <v>0</v>
       </c>
       <c r="C33">
-        <v>0.02782971538947907</v>
+        <v>0.07162353270483773</v>
       </c>
       <c r="D33">
-        <v>0.3215023059479291</v>
+        <v>0.01064243788129301</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -967,10 +967,10 @@
         <v>0</v>
       </c>
       <c r="C34">
-        <v>0.07162353270483773</v>
+        <v>0.2045972503771621</v>
       </c>
       <c r="D34">
-        <v>0.01064243788129301</v>
+        <v>1.771735228659869E-13</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="C35">
-        <v>-0.001178186297915739</v>
+        <v>-0.1840675505765382</v>
       </c>
       <c r="D35">
-        <v>0.9665287451927558</v>
+        <v>3.783255740618084E-11</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -995,10 +995,10 @@
         <v>0</v>
       </c>
       <c r="C36">
-        <v>-0.1840675505765382</v>
+        <v>0.116408059406549</v>
       </c>
       <c r="D36">
-        <v>3.783255740618084E-11</v>
+        <v>3.180513501099746E-05</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1023,10 +1023,10 @@
         <v>0</v>
       </c>
       <c r="C38">
-        <v>0.116408059406549</v>
+        <v>0.06899528972260857</v>
       </c>
       <c r="D38">
-        <v>3.180513501099747E-05</v>
+        <v>0.01388328883776795</v>
       </c>
     </row>
   </sheetData>

--- a/연구코드/results/feature_selection/sinchon/step3_univariate.xlsx
+++ b/연구코드/results/feature_selection/sinchon/step3_univariate.xlsx
@@ -103,40 +103,40 @@
     <t>IQR</t>
   </si>
   <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>signal_energy</t>
+  </si>
+  <si>
+    <t>peak_std_height</t>
+  </si>
+  <si>
+    <t>slope_std</t>
+  </si>
+  <si>
+    <t>slope_mean</t>
+  </si>
+  <si>
     <t>peak_last_pos</t>
   </si>
   <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>signal_energy</t>
-  </si>
-  <si>
-    <t>peak_std_height</t>
+    <t>peak_main_pos</t>
   </si>
   <si>
     <t>peak_first_pos</t>
   </si>
   <si>
-    <t>min</t>
-  </si>
-  <si>
-    <t>peak_main_pos</t>
-  </si>
-  <si>
-    <t>slope_std</t>
-  </si>
-  <si>
     <t>slope_min</t>
   </si>
   <si>
+    <t>band3_energy</t>
+  </si>
+  <si>
     <t>wavelet_cD3_std</t>
-  </si>
-  <si>
-    <t>band3_energy</t>
-  </si>
-  <si>
-    <t>slope_mean</t>
   </si>
 </sst>
 </file>
@@ -578,7 +578,7 @@
         <v>0.1733840996662887</v>
       </c>
       <c r="D6">
-        <v>4.894997707133989E-10</v>
+        <v>4.894997707133988E-10</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -676,7 +676,7 @@
         <v>0.02520720991881296</v>
       </c>
       <c r="D13">
-        <v>0.3692266617451235</v>
+        <v>0.3692266617451234</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -816,7 +816,7 @@
         <v>-0.06016177884717459</v>
       </c>
       <c r="D23">
-        <v>0.03197962040409953</v>
+        <v>0.03197962040409952</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -869,10 +869,10 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>0.02782971538947907</v>
+        <v>0.2311231494201107</v>
       </c>
       <c r="D27">
-        <v>0.3215023059479291</v>
+        <v>7.126123145518417E-17</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -886,7 +886,7 @@
         <v>-0.131354028217828</v>
       </c>
       <c r="D28">
-        <v>2.618507265846387E-06</v>
+        <v>2.618507265846386E-06</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -925,10 +925,10 @@
         <v>0</v>
       </c>
       <c r="C31">
-        <v>-0.001178186297915739</v>
+        <v>0.2045972503771621</v>
       </c>
       <c r="D31">
-        <v>0.9665287451927558</v>
+        <v>1.771735228659869E-13</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -939,10 +939,10 @@
         <v>0</v>
       </c>
       <c r="C32">
-        <v>0.2311231494201107</v>
+        <v>0.06899528972260857</v>
       </c>
       <c r="D32">
-        <v>7.126123145518417E-17</v>
+        <v>0.01388328883776795</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -953,10 +953,10 @@
         <v>0</v>
       </c>
       <c r="C33">
-        <v>0.07162353270483773</v>
+        <v>0.02782971538947907</v>
       </c>
       <c r="D33">
-        <v>0.01064243788129301</v>
+        <v>0.3215023059479291</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -967,10 +967,10 @@
         <v>0</v>
       </c>
       <c r="C34">
-        <v>0.2045972503771621</v>
+        <v>0.07162353270483773</v>
       </c>
       <c r="D34">
-        <v>1.771735228659869E-13</v>
+        <v>0.01064243788129301</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="C35">
-        <v>-0.1840675505765382</v>
+        <v>-0.001178186297915739</v>
       </c>
       <c r="D35">
-        <v>3.783255740618084E-11</v>
+        <v>0.9665287451927558</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -995,10 +995,10 @@
         <v>0</v>
       </c>
       <c r="C36">
-        <v>0.116408059406549</v>
+        <v>-0.1840675505765382</v>
       </c>
       <c r="D36">
-        <v>3.180513501099746E-05</v>
+        <v>3.783255740618084E-11</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1023,10 +1023,10 @@
         <v>0</v>
       </c>
       <c r="C38">
-        <v>0.06899528972260857</v>
+        <v>0.116408059406549</v>
       </c>
       <c r="D38">
-        <v>0.01388328883776795</v>
+        <v>3.180513501099747E-05</v>
       </c>
     </row>
   </sheetData>
